--- a/TestData/LoginData.xlsx
+++ b/TestData/LoginData.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\latestEclipse\ContactMnagementAutomation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A068445-73C3-4B2E-BF21-B4DBD8D6F1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7499C4C1-3F3A-4D80-AEEF-F22151B401FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D02A23C8-F3CF-4E91-ADA2-7371915555BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -53,9 +38,6 @@
     <t>Valid login</t>
   </si>
   <si>
-    <t>cmsautomation2025A2gmail.com</t>
-  </si>
-  <si>
     <t>Cms@12345</t>
   </si>
   <si>
@@ -87,6 +69,9 @@
   </si>
   <si>
     <t>Verify masking</t>
+  </si>
+  <si>
+    <t>cmsautomation2025@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -505,70 +490,70 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -577,6 +562,9 @@
     <hyperlink ref="D3" r:id="rId2" xr:uid="{3319C819-0AC0-4C1A-BFD7-07D81453B35D}"/>
     <hyperlink ref="D6" r:id="rId3" xr:uid="{CD751CF2-8564-4C58-AD8B-B212BE0D0B4E}"/>
     <hyperlink ref="D7" r:id="rId4" xr:uid="{0A4CA4F2-49A2-479B-A0CB-2C208383E042}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{9FA9052A-0AE2-4A22-9724-61ECE52349B1}"/>
+    <hyperlink ref="C4" r:id="rId6" xr:uid="{38A54B9D-4719-471A-B364-27F399616570}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{8C5337CD-8533-4810-A317-7253132723A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
